--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134629192</v>
+        <v>137172885</v>
       </c>
       <c r="B83" t="n">
-        <v>58260</v>
+        <v>43500</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10006,37 +10006,50 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103012</v>
+        <v>101242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700257</v>
+        <v>700334</v>
       </c>
       <c r="R83" t="n">
-        <v>6359091</v>
+        <v>6359038</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10060,22 +10073,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10084,33 +10087,38 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629192</t>
+          <t>https://artportalen.se/Sighting/137172885</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134629189</v>
+        <v>137172912</v>
       </c>
       <c r="B84" t="n">
-        <v>58134</v>
+        <v>43500</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10118,37 +10126,50 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103020</v>
+        <v>101242</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700255</v>
+        <v>700333</v>
       </c>
       <c r="R84" t="n">
-        <v>6359112</v>
+        <v>6359054</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10172,22 +10193,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10196,33 +10207,38 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Via Margaret Rainey</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629189</t>
+          <t>https://artportalen.se/Sighting/137172912</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>111589164</v>
+        <v>134629192</v>
       </c>
       <c r="B85" t="n">
-        <v>5479</v>
+        <v>58260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10230,62 +10246,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>105894</v>
+        <v>103012</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700322</v>
+        <v>700257</v>
       </c>
       <c r="R85" t="n">
-        <v>6359100</v>
+        <v>6359091</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10309,12 +10300,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10323,86 +10324,71 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111589164</t>
+          <t>https://artportalen.se/Sighting/134629192</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>116259087</v>
+        <v>134629189</v>
       </c>
       <c r="B86" t="n">
-        <v>99035</v>
+        <v>58134</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219790</v>
+        <v>103020</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700256</v>
+        <v>700255</v>
       </c>
       <c r="R86" t="n">
-        <v>6359045</v>
+        <v>6359112</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10426,12 +10412,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10442,58 +10438,53 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Via Margaret Rainey</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116259087</t>
+          <t>https://artportalen.se/Sighting/134629189</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126300257</v>
+        <v>111589164</v>
       </c>
       <c r="B87" t="n">
-        <v>99096</v>
+        <v>5479</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>105894</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10501,19 +10492,40 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700247</v>
+        <v>700322</v>
       </c>
       <c r="R87" t="n">
-        <v>6359114</v>
+        <v>6359100</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10537,12 +10549,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10551,38 +10563,34 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300257</t>
+          <t>https://artportalen.se/Sighting/111589164</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126514044</v>
+        <v>116259087</v>
       </c>
       <c r="B88" t="n">
-        <v>99096</v>
+        <v>99035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10590,21 +10598,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10612,19 +10620,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700215</v>
+        <v>700256</v>
       </c>
       <c r="R88" t="n">
-        <v>6359155</v>
+        <v>6359045</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10648,12 +10666,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10667,33 +10685,33 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Hästbetad blandskog</t>
+          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514044</t>
+          <t>https://artportalen.se/Sighting/116259087</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126300256</v>
+        <v>126300257</v>
       </c>
       <c r="B89" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10701,24 +10719,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -10791,16 +10813,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300256</t>
+          <t>https://artportalen.se/Sighting/126300257</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126300258</v>
+        <v>126514044</v>
       </c>
       <c r="B90" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10808,26 +10830,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10836,13 +10858,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700247</v>
+        <v>700215</v>
       </c>
       <c r="R90" t="n">
-        <v>6359105</v>
+        <v>6359155</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10902,13 +10924,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300258</t>
+          <t>https://artportalen.se/Sighting/126514044</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126300265</v>
+        <v>126300256</v>
       </c>
       <c r="B91" t="n">
         <v>99142</v>
@@ -10946,10 +10968,10 @@
         <v>700247</v>
       </c>
       <c r="R91" t="n">
-        <v>6359082</v>
+        <v>6359114</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11009,13 +11031,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300265</t>
+          <t>https://artportalen.se/Sighting/126300256</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126300268</v>
+        <v>126300258</v>
       </c>
       <c r="B92" t="n">
         <v>99142</v>
@@ -11043,20 +11065,24 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700265</v>
+        <v>700247</v>
       </c>
       <c r="R92" t="n">
-        <v>6359056</v>
+        <v>6359105</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11116,13 +11142,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300268</t>
+          <t>https://artportalen.se/Sighting/126300258</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126300273</v>
+        <v>126300265</v>
       </c>
       <c r="B93" t="n">
         <v>99142</v>
@@ -11150,24 +11176,20 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700275</v>
+        <v>700247</v>
       </c>
       <c r="R93" t="n">
-        <v>6359045</v>
+        <v>6359082</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11227,13 +11249,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300273</t>
+          <t>https://artportalen.se/Sighting/126300265</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126514045</v>
+        <v>126300268</v>
       </c>
       <c r="B94" t="n">
         <v>99142</v>
@@ -11268,13 +11290,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700215</v>
+        <v>700265</v>
       </c>
       <c r="R94" t="n">
-        <v>6359155</v>
+        <v>6359056</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11334,13 +11356,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514045</t>
+          <t>https://artportalen.se/Sighting/126300268</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126514049</v>
+        <v>126300273</v>
       </c>
       <c r="B95" t="n">
         <v>99142</v>
@@ -11368,20 +11390,24 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700235</v>
+        <v>700275</v>
       </c>
       <c r="R95" t="n">
-        <v>6359147</v>
+        <v>6359045</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11441,16 +11467,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514049</t>
+          <t>https://artportalen.se/Sighting/126300273</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134628528</v>
+        <v>126514045</v>
       </c>
       <c r="B96" t="n">
-        <v>99219</v>
+        <v>99142</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11478,17 +11504,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700250</v>
+        <v>700215</v>
       </c>
       <c r="R96" t="n">
-        <v>6359173</v>
+        <v>6359155</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11512,22 +11538,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11538,31 +11554,36 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134628528</t>
+          <t>https://artportalen.se/Sighting/126514045</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134629174</v>
+        <v>126514049</v>
       </c>
       <c r="B97" t="n">
-        <v>99219</v>
+        <v>99142</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11590,17 +11611,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700262</v>
+        <v>700235</v>
       </c>
       <c r="R97" t="n">
-        <v>6359042</v>
+        <v>6359147</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11624,22 +11645,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11650,28 +11661,33 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629174</t>
+          <t>https://artportalen.se/Sighting/126514049</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134629183</v>
+        <v>134628528</v>
       </c>
       <c r="B98" t="n">
         <v>99219</v>
@@ -11702,14 +11718,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700205</v>
+        <v>700250</v>
       </c>
       <c r="R98" t="n">
-        <v>6359141</v>
+        <v>6359173</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11741,7 +11757,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11751,7 +11767,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11766,24 +11782,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629183</t>
+          <t>https://artportalen.se/Sighting/134628528</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134629187</v>
+        <v>134629174</v>
       </c>
       <c r="B99" t="n">
         <v>99219</v>
@@ -11818,10 +11834,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700230</v>
+        <v>700262</v>
       </c>
       <c r="R99" t="n">
-        <v>6359151</v>
+        <v>6359042</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11853,7 +11869,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11863,12 +11879,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11894,16 +11905,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629187</t>
+          <t>https://artportalen.se/Sighting/134629174</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126300267</v>
+        <v>134629183</v>
       </c>
       <c r="B100" t="n">
-        <v>99141</v>
+        <v>99219</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,41 +11922,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700257</v>
+        <v>700205</v>
       </c>
       <c r="R100" t="n">
-        <v>6359067</v>
+        <v>6359141</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11969,12 +11976,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11985,36 +12002,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300267</t>
+          <t>https://artportalen.se/Sighting/134629183</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134629170</v>
+        <v>134629187</v>
       </c>
       <c r="B101" t="n">
-        <v>99230</v>
+        <v>99219</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,21 +12034,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12046,10 +12058,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700270</v>
+        <v>700230</v>
       </c>
       <c r="R101" t="n">
-        <v>6359038</v>
+        <v>6359151</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12081,7 +12093,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12091,7 +12103,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12117,62 +12134,58 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629170</t>
+          <t>https://artportalen.se/Sighting/134629187</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>97960624</v>
+        <v>126300267</v>
       </c>
       <c r="B102" t="n">
-        <v>110078</v>
+        <v>99141</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700333</v>
+        <v>700257</v>
       </c>
       <c r="R102" t="n">
-        <v>6359040</v>
+        <v>6359067</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12196,12 +12209,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12210,83 +12223,73 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97960624</t>
+          <t>https://artportalen.se/Sighting/126300267</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2760594</v>
+        <v>134629170</v>
       </c>
       <c r="B103" t="n">
-        <v>110117</v>
+        <v>99230</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220320</v>
+        <v>219874</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700332</v>
+        <v>700270</v>
       </c>
       <c r="R103" t="n">
-        <v>6359036</v>
+        <v>6359038</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12313,17 +12316,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12334,36 +12342,31 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Stigkant</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2760594</t>
+          <t>https://artportalen.se/Sighting/134629170</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>16230167</v>
+        <v>97960624</v>
       </c>
       <c r="B104" t="n">
-        <v>110117</v>
+        <v>110078</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12371,16 +12374,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12392,10 +12395,11 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Russparken, parkeringen 100m N, Gtl</t>
@@ -12432,12 +12436,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12446,6 +12450,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12463,13 +12468,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16230167</t>
+          <t>https://artportalen.se/Sighting/97960624</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>16500486</v>
+        <v>2760594</v>
       </c>
       <c r="B105" t="n">
         <v>110117</v>
@@ -12497,23 +12502,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700339</v>
+        <v>700332</v>
       </c>
       <c r="R105" t="n">
-        <v>6359017</v>
+        <v>6359036</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12532,17 +12548,22 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2008-09-04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12553,28 +12574,33 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Stigkant</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
+          <t>Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16500486</t>
+          <t>https://artportalen.se/Sighting/2760594</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>69716937</v>
+        <v>16230167</v>
       </c>
       <c r="B106" t="n">
         <v>110117</v>
@@ -12603,24 +12629,26 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700329</v>
+        <v>700333</v>
       </c>
       <c r="R106" t="n">
-        <v>6359034</v>
+        <v>6359040</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12644,12 +12672,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12660,33 +12688,28 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69716937</t>
+          <t>https://artportalen.se/Sighting/16230167</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>105024185</v>
+        <v>16500486</v>
       </c>
       <c r="B107" t="n">
         <v>110117</v>
@@ -12714,29 +12737,23 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700333</v>
+        <v>700339</v>
       </c>
       <c r="R107" t="n">
-        <v>6359035</v>
+        <v>6359017</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12755,22 +12772,17 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12785,28 +12797,24 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105024185</t>
+          <t>https://artportalen.se/Sighting/16500486</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>105024186</v>
+        <v>69716937</v>
       </c>
       <c r="B108" t="n">
         <v>110117</v>
@@ -12834,26 +12842,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700323</v>
+        <v>700329</v>
       </c>
       <c r="R108" t="n">
-        <v>6359035</v>
+        <v>6359034</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12880,12 +12884,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12899,34 +12903,30 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Körvägkant.</t>
+          <t>Fuktig ängsmark</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105024186</t>
+          <t>https://artportalen.se/Sighting/69716937</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>105024198</v>
+        <v>105024185</v>
       </c>
       <c r="B109" t="n">
         <v>110117</v>
@@ -12966,17 +12966,17 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Lilla Korsgatan N, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
         <v>700333</v>
       </c>
       <c r="R109" t="n">
-        <v>6359015</v>
+        <v>6359035</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12995,22 +12995,22 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
+          <t>2008-07-26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
+          <t>2008-07-26</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>57 stänglar. Ungefärlig koordinat.</t>
+          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13021,11 +13021,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>Stig i kalktallskog, delvis sandunderlag</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13045,13 +13040,13 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105024198</t>
+          <t>https://artportalen.se/Sighting/105024185</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>111587690</v>
+        <v>105024186</v>
       </c>
       <c r="B110" t="n">
         <v>110117</v>
@@ -13081,34 +13076,27 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700319</v>
+        <v>700323</v>
       </c>
       <c r="R110" t="n">
-        <v>6359038</v>
+        <v>6359035</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13132,12 +13120,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13146,31 +13134,39 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Körvägkant.</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111587690</t>
+          <t>https://artportalen.se/Sighting/105024186</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126312506</v>
+        <v>105024198</v>
       </c>
       <c r="B111" t="n">
         <v>110117</v>
@@ -13200,7 +13196,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13208,21 +13204,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan, Gtl</t>
+          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700335</v>
+        <v>700333</v>
       </c>
       <c r="R111" t="n">
-        <v>6359040</v>
+        <v>6359015</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13244,17 +13235,22 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2006-07-04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2006-07-04</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>57 stänglar. Ungefärlig koordinat.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13265,69 +13261,94 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Stig i kalktallskog, delvis sandunderlag</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Felicia Wikinger</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Felicia Wikinger, Teo Jernkvist</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126312506</t>
+          <t>https://artportalen.se/Sighting/105024198</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>116259105</v>
+        <v>111587690</v>
       </c>
       <c r="B112" t="n">
-        <v>101326</v>
+        <v>110117</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>220320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700330</v>
+        <v>700319</v>
       </c>
       <c r="R112" t="n">
-        <v>6359014</v>
+        <v>6359038</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13351,17 +13372,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Spridd i hela skogen.</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13370,75 +13386,86 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116259105</t>
+          <t>https://artportalen.se/Sighting/111587690</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126300259</v>
+        <v>126312506</v>
       </c>
       <c r="B113" t="n">
-        <v>99036</v>
+        <v>110117</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223591</v>
+        <v>220320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Lilla Korsgatan, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700247</v>
+        <v>700335</v>
       </c>
       <c r="R113" t="n">
-        <v>6359105</v>
+        <v>6359040</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13462,12 +13489,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13478,36 +13505,31 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Felicia Wikinger</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Felicia Wikinger, Teo Jernkvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300259</t>
+          <t>https://artportalen.se/Sighting/126312506</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126300263</v>
+        <v>116259105</v>
       </c>
       <c r="B114" t="n">
-        <v>99036</v>
+        <v>101326</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13515,41 +13537,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>223591</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>700253</v>
+        <v>700330</v>
       </c>
       <c r="R114" t="n">
-        <v>6359086</v>
+        <v>6359014</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13573,12 +13591,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13589,33 +13612,28 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300263</t>
+          <t>https://artportalen.se/Sighting/116259105</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126300266</v>
+        <v>126300259</v>
       </c>
       <c r="B115" t="n">
         <v>99036</v>
@@ -13645,7 +13663,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13657,10 +13675,10 @@
         <v>700247</v>
       </c>
       <c r="R115" t="n">
-        <v>6359082</v>
+        <v>6359105</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13720,13 +13738,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300266</t>
+          <t>https://artportalen.se/Sighting/126300259</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126300270</v>
+        <v>126300263</v>
       </c>
       <c r="B116" t="n">
         <v>99036</v>
@@ -13754,17 +13772,21 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700265</v>
+        <v>700253</v>
       </c>
       <c r="R116" t="n">
-        <v>6359056</v>
+        <v>6359086</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -13827,13 +13849,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300270</t>
+          <t>https://artportalen.se/Sighting/126300263</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126300272</v>
+        <v>126300266</v>
       </c>
       <c r="B117" t="n">
         <v>99036</v>
@@ -13863,7 +13885,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13872,13 +13894,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700275</v>
+        <v>700247</v>
       </c>
       <c r="R117" t="n">
-        <v>6359045</v>
+        <v>6359082</v>
       </c>
       <c r="S117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13938,13 +13960,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126300272</t>
+          <t>https://artportalen.se/Sighting/126300266</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126514047</v>
+        <v>126300270</v>
       </c>
       <c r="B118" t="n">
         <v>99036</v>
@@ -13979,13 +14001,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700215</v>
+        <v>700265</v>
       </c>
       <c r="R118" t="n">
-        <v>6359155</v>
+        <v>6359056</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14045,16 +14067,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514047</t>
+          <t>https://artportalen.se/Sighting/126300270</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134628531</v>
+        <v>126300272</v>
       </c>
       <c r="B119" t="n">
-        <v>99113</v>
+        <v>99036</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14079,20 +14101,24 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700192</v>
+        <v>700275</v>
       </c>
       <c r="R119" t="n">
-        <v>6359150</v>
+        <v>6359045</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14116,22 +14142,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14142,31 +14158,36 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134628531</t>
+          <t>https://artportalen.se/Sighting/126300272</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134629175</v>
+        <v>126514047</v>
       </c>
       <c r="B120" t="n">
-        <v>99113</v>
+        <v>99036</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14194,17 +14215,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700259</v>
+        <v>700215</v>
       </c>
       <c r="R120" t="n">
-        <v>6359029</v>
+        <v>6359155</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14228,22 +14249,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14254,28 +14265,33 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629175</t>
+          <t>https://artportalen.se/Sighting/126514047</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134629176</v>
+        <v>134628531</v>
       </c>
       <c r="B121" t="n">
         <v>99113</v>
@@ -14306,17 +14322,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700225</v>
+        <v>700192</v>
       </c>
       <c r="R121" t="n">
-        <v>6359027</v>
+        <v>6359150</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14345,7 +14361,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14355,7 +14371,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14370,24 +14386,24 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629176</t>
+          <t>https://artportalen.se/Sighting/134628531</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134629180</v>
+        <v>134629175</v>
       </c>
       <c r="B122" t="n">
         <v>99113</v>
@@ -14422,10 +14438,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700189</v>
+        <v>700259</v>
       </c>
       <c r="R122" t="n">
-        <v>6359091</v>
+        <v>6359029</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14457,7 +14473,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14467,7 +14483,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14493,13 +14509,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629180</t>
+          <t>https://artportalen.se/Sighting/134629175</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134629194</v>
+        <v>134629176</v>
       </c>
       <c r="B123" t="n">
         <v>99113</v>
@@ -14534,13 +14550,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700257</v>
+        <v>700225</v>
       </c>
       <c r="R123" t="n">
-        <v>6359091</v>
+        <v>6359027</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14569,7 +14585,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14579,7 +14595,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14605,16 +14621,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134629194</t>
+          <t>https://artportalen.se/Sighting/134629176</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126300254</v>
+        <v>134629180</v>
       </c>
       <c r="B124" t="n">
-        <v>99155</v>
+        <v>99113</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14622,41 +14638,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>700231</v>
+        <v>700189</v>
       </c>
       <c r="R124" t="n">
-        <v>6359136</v>
+        <v>6359091</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14680,12 +14692,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14696,25 +14718,243 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629180</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>134629194</v>
+      </c>
+      <c r="B125" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Gerums Likmunds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>700257</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6359091</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629194</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>126300254</v>
+      </c>
+      <c r="B126" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>700231</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6359136</v>
+      </c>
+      <c r="S126" t="n">
+        <v>4</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126300254</t>
         </is>
@@ -14845,6 +15085,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>137172885</v>
       </c>
       <c r="B83" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>137172912</v>
       </c>
       <c r="B84" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>137172885</v>
       </c>
       <c r="B83" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>137172912</v>
       </c>
       <c r="B84" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -10029,11 +10029,7 @@
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -10149,11 +10145,7 @@
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>137172885</v>
       </c>
       <c r="B83" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>137172912</v>
       </c>
       <c r="B84" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>137172885</v>
       </c>
       <c r="B83" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>137172912</v>
       </c>
       <c r="B84" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
